--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Unpaid_Bills.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Unpaid_Bills.xlsx
@@ -615,7 +615,7 @@
         <v>152282.54</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>127278.64</v>
+        <v>127537.01</v>
       </c>
     </row>
     <row r="14">
@@ -628,7 +628,7 @@
         <v>152282.54</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>127278.64</v>
+        <v>127537.01</v>
       </c>
     </row>
     <row r="15">
@@ -714,10 +714,10 @@
         <v>-22</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>7989</v>
+        <v>7730.63</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>7989</v>
+        <v>7730.63</v>
       </c>
     </row>
     <row r="20">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>7989</v>
+        <v>7730.63</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>7989</v>
+        <v>7730.63</v>
       </c>
     </row>
     <row r="21">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>314424.08</v>
+        <v>314165.71</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>287640.18</v>

--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Unpaid_Bills.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Unpaid_Bills.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -615,7 +615,7 @@
         <v>152282.54</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>127537.01</v>
+        <v>128030.76</v>
       </c>
     </row>
     <row r="14">
@@ -628,7 +628,7 @@
         <v>152282.54</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>127537.01</v>
+        <v>128030.76</v>
       </c>
     </row>
     <row r="15">
@@ -714,10 +714,10 @@
         <v>-22</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>7730.63</v>
+        <v>7236.88</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>7730.63</v>
+        <v>7236.88</v>
       </c>
     </row>
     <row r="20">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>7730.63</v>
+        <v>7236.88</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>7730.63</v>
+        <v>7236.88</v>
       </c>
     </row>
     <row r="21">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>314165.71</v>
+        <v>313671.96</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>287640.18</v>

--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Unpaid_Bills.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Unpaid_Bills.xlsx
@@ -561,10 +561,10 @@
         <v>-4</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>60913.03</v>
+        <v>60717</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>60913.03</v>
+        <v>60717</v>
       </c>
     </row>
     <row r="11">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>60913.03</v>
+        <v>60717</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>60913.03</v>
+        <v>60717</v>
       </c>
     </row>
     <row r="12">
@@ -612,10 +612,10 @@
         <v>-4</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>152282.54</v>
+        <v>151792.54</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>128030.76</v>
+        <v>128520.78</v>
       </c>
     </row>
     <row r="14">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="G14" s="1" t="n">
-        <v>152282.54</v>
+        <v>151792.54</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>128030.76</v>
+        <v>128520.78</v>
       </c>
     </row>
     <row r="15">
@@ -663,10 +663,10 @@
         <v>-4</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>91369.50999999999</v>
+        <v>91075.52</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>91369.50999999999</v>
+        <v>91075.52</v>
       </c>
     </row>
     <row r="17">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>91369.50999999999</v>
+        <v>91075.52</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>91369.50999999999</v>
+        <v>91075.52</v>
       </c>
     </row>
     <row r="18">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>313671.96</v>
+        <v>312691.94</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>287640.18</v>
